--- a/Tables/G_ValTable.xlsx
+++ b/Tables/G_ValTable.xlsx
@@ -391,7 +391,7 @@
     <col customWidth="1" min="4" max="25" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -428,7 +428,7 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" ht="15.0" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -465,7 +465,7 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" ht="15.0" customHeight="1">
+    <row r="3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -502,7 +502,7 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" ht="15.0" customHeight="1">
+    <row r="4">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -539,7 +539,7 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
     </row>
-    <row r="5" ht="15.0" customHeight="1">
+    <row r="5">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -576,7 +576,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" ht="15.0" customHeight="1">
+    <row r="6">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
@@ -613,7 +613,7 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
     </row>
-    <row r="7" ht="15.0" customHeight="1">
+    <row r="7">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -650,7 +650,7 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8" ht="15.0" customHeight="1">
+    <row r="8">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -687,7 +687,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" ht="15.0" customHeight="1">
+    <row r="9">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -724,7 +724,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" ht="15.0" customHeight="1">
+    <row r="10">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -761,7 +761,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" ht="15.0" customHeight="1">
+    <row r="11">
       <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
@@ -798,7 +798,7 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
     </row>
-    <row r="12" ht="15.0" customHeight="1">
+    <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -825,7 +825,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" ht="15.0" customHeight="1">
+    <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -852,7 +852,7 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
     </row>
-    <row r="14" ht="15.0" customHeight="1">
+    <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -879,7 +879,7 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" ht="15.0" customHeight="1">
+    <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -906,7 +906,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" ht="15.0" customHeight="1">
+    <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -933,7 +933,7 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" ht="15.0" customHeight="1">
+    <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -960,7 +960,7 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
     </row>
-    <row r="18" ht="15.0" customHeight="1">
+    <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -987,7 +987,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" ht="15.0" customHeight="1">
+    <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1014,7 +1014,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" ht="15.0" customHeight="1">
+    <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1041,7 +1041,7 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
     </row>
-    <row r="21" ht="15.0" customHeight="1">
+    <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1068,7 +1068,7 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" ht="15.0" customHeight="1">
+    <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1095,7 +1095,7 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" ht="15.0" customHeight="1">
+    <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1122,7 +1122,7 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" ht="15.0" customHeight="1">
+    <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1149,7 +1149,7 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" ht="15.0" customHeight="1">
+    <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1176,7 +1176,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" ht="15.0" customHeight="1">
+    <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1203,7 +1203,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" ht="15.0" customHeight="1">
+    <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1230,7 +1230,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" ht="15.0" customHeight="1">
+    <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1257,7 +1257,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" ht="15.0" customHeight="1">
+    <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1284,7 +1284,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" ht="15.0" customHeight="1">
+    <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1311,7 +1311,7 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" ht="15.0" customHeight="1">
+    <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1338,7 +1338,7 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" ht="15.0" customHeight="1">
+    <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1365,7 +1365,7 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" ht="15.0" customHeight="1">
+    <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1392,7 +1392,7 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" ht="15.0" customHeight="1">
+    <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1419,7 +1419,7 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35" ht="15.0" customHeight="1">
+    <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1446,7 +1446,7 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" ht="15.0" customHeight="1">
+    <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1473,7 +1473,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" ht="15.0" customHeight="1">
+    <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1500,7 +1500,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" ht="15.0" customHeight="1">
+    <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1527,7 +1527,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" ht="15.0" customHeight="1">
+    <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1554,7 +1554,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40" ht="15.0" customHeight="1">
+    <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1581,7 +1581,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41" ht="15.0" customHeight="1">
+    <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1608,7 +1608,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
     </row>
-    <row r="42" ht="15.0" customHeight="1">
+    <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1635,7 +1635,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43" ht="15.0" customHeight="1">
+    <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1662,7 +1662,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" ht="15.0" customHeight="1">
+    <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1689,7 +1689,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45" ht="15.0" customHeight="1">
+    <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1716,7 +1716,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46" ht="15.0" customHeight="1">
+    <row r="46">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1743,7 +1743,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
     </row>
-    <row r="47" ht="15.0" customHeight="1">
+    <row r="47">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1770,7 +1770,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" ht="15.0" customHeight="1">
+    <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1797,7 +1797,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" ht="15.0" customHeight="1">
+    <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1824,7 +1824,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
     </row>
-    <row r="50" ht="15.0" customHeight="1">
+    <row r="50">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1851,7 +1851,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" ht="15.0" customHeight="1">
+    <row r="51">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1878,7 +1878,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52" ht="15.0" customHeight="1">
+    <row r="52">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1905,7 +1905,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" ht="15.0" customHeight="1">
+    <row r="53">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1932,7 +1932,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" ht="15.0" customHeight="1">
+    <row r="54">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1959,7 +1959,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" ht="15.0" customHeight="1">
+    <row r="55">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1986,7 +1986,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
     </row>
-    <row r="56" ht="15.0" customHeight="1">
+    <row r="56">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2013,7 +2013,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
     </row>
-    <row r="57" ht="15.0" customHeight="1">
+    <row r="57">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2040,7 +2040,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58" ht="15.0" customHeight="1">
+    <row r="58">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2067,7 +2067,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" ht="15.0" customHeight="1">
+    <row r="59">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2094,7 +2094,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" ht="15.0" customHeight="1">
+    <row r="60">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2121,7 +2121,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" ht="15.0" customHeight="1">
+    <row r="61">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2148,7 +2148,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" ht="15.0" customHeight="1">
+    <row r="62">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2175,7 +2175,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" ht="15.0" customHeight="1">
+    <row r="63">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2202,7 +2202,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64" ht="15.0" customHeight="1">
+    <row r="64">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2229,7 +2229,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" ht="15.0" customHeight="1">
+    <row r="65">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2256,7 +2256,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" ht="15.0" customHeight="1">
+    <row r="66">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2283,7 +2283,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" ht="15.0" customHeight="1">
+    <row r="67">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2310,7 +2310,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68" ht="15.0" customHeight="1">
+    <row r="68">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2337,7 +2337,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" ht="15.0" customHeight="1">
+    <row r="69">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2364,7 +2364,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" ht="15.0" customHeight="1">
+    <row r="70">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2391,7 +2391,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71" ht="15.0" customHeight="1">
+    <row r="71">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2418,7 +2418,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" ht="15.0" customHeight="1">
+    <row r="72">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2445,7 +2445,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" ht="15.0" customHeight="1">
+    <row r="73">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2472,7 +2472,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" ht="15.0" customHeight="1">
+    <row r="74">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2499,7 +2499,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75" ht="15.0" customHeight="1">
+    <row r="75">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2526,7 +2526,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76" ht="15.0" customHeight="1">
+    <row r="76">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2553,7 +2553,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77" ht="15.0" customHeight="1">
+    <row r="77">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2580,7 +2580,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78" ht="15.0" customHeight="1">
+    <row r="78">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2607,7 +2607,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" ht="15.0" customHeight="1">
+    <row r="79">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2634,7 +2634,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80" ht="15.0" customHeight="1">
+    <row r="80">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2661,7 +2661,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" ht="15.0" customHeight="1">
+    <row r="81">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2688,7 +2688,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" ht="15.0" customHeight="1">
+    <row r="82">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2715,7 +2715,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" ht="15.0" customHeight="1">
+    <row r="83">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2742,7 +2742,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84" ht="15.0" customHeight="1">
+    <row r="84">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2769,7 +2769,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85" ht="15.0" customHeight="1">
+    <row r="85">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2796,7 +2796,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" ht="15.0" customHeight="1">
+    <row r="86">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2823,7 +2823,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" ht="15.0" customHeight="1">
+    <row r="87">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2850,7 +2850,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88" ht="15.0" customHeight="1">
+    <row r="88">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2877,7 +2877,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89" ht="15.0" customHeight="1">
+    <row r="89">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2904,7 +2904,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" ht="15.0" customHeight="1">
+    <row r="90">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2931,7 +2931,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91" ht="15.0" customHeight="1">
+    <row r="91">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2958,7 +2958,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" ht="15.0" customHeight="1">
+    <row r="92">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2985,7 +2985,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" ht="15.0" customHeight="1">
+    <row r="93">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3012,7 +3012,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" ht="15.0" customHeight="1">
+    <row r="94">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3039,7 +3039,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" ht="15.0" customHeight="1">
+    <row r="95">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3066,7 +3066,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" ht="15.0" customHeight="1">
+    <row r="96">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3093,7 +3093,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" ht="15.0" customHeight="1">
+    <row r="97">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3120,7 +3120,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" ht="15.0" customHeight="1">
+    <row r="98">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3147,7 +3147,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99" ht="15.0" customHeight="1">
+    <row r="99">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3174,7 +3174,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" ht="15.0" customHeight="1">
+    <row r="100">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3201,7 +3201,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" ht="15.0" customHeight="1">
+    <row r="101">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3228,7 +3228,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" ht="15.0" customHeight="1">
+    <row r="102">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3255,7 +3255,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" ht="15.0" customHeight="1">
+    <row r="103">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3282,7 +3282,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" ht="15.0" customHeight="1">
+    <row r="104">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3309,7 +3309,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" ht="15.0" customHeight="1">
+    <row r="105">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3336,7 +3336,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106" ht="15.0" customHeight="1">
+    <row r="106">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3363,7 +3363,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107" ht="15.0" customHeight="1">
+    <row r="107">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3390,7 +3390,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108" ht="15.0" customHeight="1">
+    <row r="108">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3417,7 +3417,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109" ht="15.0" customHeight="1">
+    <row r="109">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3444,7 +3444,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110" ht="15.0" customHeight="1">
+    <row r="110">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3471,7 +3471,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111" ht="15.0" customHeight="1">
+    <row r="111">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3498,7 +3498,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" ht="15.0" customHeight="1">
+    <row r="112">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3525,7 +3525,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113" ht="15.0" customHeight="1">
+    <row r="113">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3552,7 +3552,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114" ht="15.0" customHeight="1">
+    <row r="114">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3579,7 +3579,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115" ht="15.0" customHeight="1">
+    <row r="115">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3606,7 +3606,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116" ht="15.0" customHeight="1">
+    <row r="116">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3633,7 +3633,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117" ht="15.0" customHeight="1">
+    <row r="117">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3660,7 +3660,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118" ht="15.0" customHeight="1">
+    <row r="118">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3687,7 +3687,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119" ht="15.0" customHeight="1">
+    <row r="119">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3714,7 +3714,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120" ht="15.0" customHeight="1">
+    <row r="120">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3741,7 +3741,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121" ht="15.0" customHeight="1">
+    <row r="121">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3768,7 +3768,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122" ht="15.0" customHeight="1">
+    <row r="122">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3795,7 +3795,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123" ht="15.0" customHeight="1">
+    <row r="123">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3822,7 +3822,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124" ht="15.0" customHeight="1">
+    <row r="124">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3849,7 +3849,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125" ht="15.0" customHeight="1">
+    <row r="125">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3876,7 +3876,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126" ht="15.0" customHeight="1">
+    <row r="126">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3903,7 +3903,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127" ht="15.0" customHeight="1">
+    <row r="127">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3930,7 +3930,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128" ht="15.0" customHeight="1">
+    <row r="128">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3957,7 +3957,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129" ht="15.0" customHeight="1">
+    <row r="129">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3984,7 +3984,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" ht="15.0" customHeight="1">
+    <row r="130">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4011,7 +4011,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131" ht="15.0" customHeight="1">
+    <row r="131">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4038,7 +4038,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132" ht="15.0" customHeight="1">
+    <row r="132">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4065,7 +4065,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133" ht="15.0" customHeight="1">
+    <row r="133">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4092,7 +4092,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134" ht="15.0" customHeight="1">
+    <row r="134">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4119,7 +4119,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135" ht="15.0" customHeight="1">
+    <row r="135">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4146,7 +4146,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136" ht="15.0" customHeight="1">
+    <row r="136">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4173,7 +4173,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137" ht="15.0" customHeight="1">
+    <row r="137">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4200,7 +4200,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138" ht="15.0" customHeight="1">
+    <row r="138">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4227,7 +4227,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139" ht="15.0" customHeight="1">
+    <row r="139">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4254,7 +4254,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140" ht="15.0" customHeight="1">
+    <row r="140">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4281,7 +4281,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141" ht="15.0" customHeight="1">
+    <row r="141">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4308,7 +4308,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142" ht="15.0" customHeight="1">
+    <row r="142">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4335,7 +4335,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143" ht="15.0" customHeight="1">
+    <row r="143">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4362,7 +4362,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144" ht="15.0" customHeight="1">
+    <row r="144">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4389,7 +4389,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145" ht="15.0" customHeight="1">
+    <row r="145">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4416,7 +4416,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146" ht="15.0" customHeight="1">
+    <row r="146">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4443,7 +4443,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147" ht="15.0" customHeight="1">
+    <row r="147">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4470,7 +4470,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148" ht="15.0" customHeight="1">
+    <row r="148">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4497,7 +4497,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149" ht="15.0" customHeight="1">
+    <row r="149">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4524,7 +4524,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150" ht="15.0" customHeight="1">
+    <row r="150">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4551,7 +4551,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151" ht="15.0" customHeight="1">
+    <row r="151">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4578,7 +4578,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152" ht="15.0" customHeight="1">
+    <row r="152">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4605,7 +4605,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153" ht="15.0" customHeight="1">
+    <row r="153">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4632,7 +4632,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154" ht="15.0" customHeight="1">
+    <row r="154">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4659,7 +4659,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155" ht="15.0" customHeight="1">
+    <row r="155">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4686,7 +4686,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156" ht="15.0" customHeight="1">
+    <row r="156">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4713,7 +4713,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157" ht="15.0" customHeight="1">
+    <row r="157">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4740,7 +4740,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158" ht="15.0" customHeight="1">
+    <row r="158">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4767,7 +4767,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159" ht="15.0" customHeight="1">
+    <row r="159">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4794,7 +4794,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160" ht="15.0" customHeight="1">
+    <row r="160">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4821,7 +4821,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161" ht="15.0" customHeight="1">
+    <row r="161">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4848,7 +4848,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162" ht="15.0" customHeight="1">
+    <row r="162">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4875,7 +4875,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163" ht="15.0" customHeight="1">
+    <row r="163">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4902,7 +4902,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164" ht="15.0" customHeight="1">
+    <row r="164">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4929,7 +4929,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165" ht="15.0" customHeight="1">
+    <row r="165">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4956,7 +4956,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166" ht="15.0" customHeight="1">
+    <row r="166">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4983,7 +4983,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167" ht="15.0" customHeight="1">
+    <row r="167">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5010,7 +5010,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168" ht="15.0" customHeight="1">
+    <row r="168">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5037,7 +5037,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169" ht="15.0" customHeight="1">
+    <row r="169">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5064,7 +5064,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170" ht="15.0" customHeight="1">
+    <row r="170">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5091,7 +5091,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171" ht="15.0" customHeight="1">
+    <row r="171">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5118,7 +5118,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172" ht="15.0" customHeight="1">
+    <row r="172">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5145,7 +5145,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173" ht="15.0" customHeight="1">
+    <row r="173">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5172,7 +5172,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174" ht="15.0" customHeight="1">
+    <row r="174">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5199,7 +5199,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175" ht="15.0" customHeight="1">
+    <row r="175">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5226,7 +5226,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176" ht="15.0" customHeight="1">
+    <row r="176">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5253,7 +5253,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177" ht="15.0" customHeight="1">
+    <row r="177">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5280,7 +5280,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178" ht="15.0" customHeight="1">
+    <row r="178">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5307,7 +5307,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179" ht="15.0" customHeight="1">
+    <row r="179">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5334,7 +5334,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180" ht="15.0" customHeight="1">
+    <row r="180">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5361,7 +5361,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181" ht="15.0" customHeight="1">
+    <row r="181">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5388,7 +5388,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182" ht="15.0" customHeight="1">
+    <row r="182">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5415,7 +5415,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183" ht="15.0" customHeight="1">
+    <row r="183">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5442,7 +5442,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184" ht="15.0" customHeight="1">
+    <row r="184">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5469,7 +5469,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185" ht="15.0" customHeight="1">
+    <row r="185">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5496,7 +5496,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186" ht="15.0" customHeight="1">
+    <row r="186">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5523,7 +5523,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187" ht="15.0" customHeight="1">
+    <row r="187">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5550,7 +5550,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188" ht="15.0" customHeight="1">
+    <row r="188">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5577,7 +5577,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189" ht="15.0" customHeight="1">
+    <row r="189">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5604,7 +5604,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190" ht="15.0" customHeight="1">
+    <row r="190">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5631,7 +5631,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191" ht="15.0" customHeight="1">
+    <row r="191">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5658,7 +5658,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192" ht="15.0" customHeight="1">
+    <row r="192">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5685,7 +5685,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" ht="15.0" customHeight="1">
+    <row r="193">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5712,7 +5712,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194" ht="15.0" customHeight="1">
+    <row r="194">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5739,7 +5739,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195" ht="15.0" customHeight="1">
+    <row r="195">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5766,7 +5766,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" ht="15.0" customHeight="1">
+    <row r="196">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5793,7 +5793,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197" ht="15.0" customHeight="1">
+    <row r="197">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5820,7 +5820,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198" ht="15.0" customHeight="1">
+    <row r="198">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5847,7 +5847,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199" ht="15.0" customHeight="1">
+    <row r="199">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5874,7 +5874,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200" ht="15.0" customHeight="1">
+    <row r="200">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5901,7 +5901,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201" ht="15.0" customHeight="1">
+    <row r="201">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5928,7 +5928,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202" ht="15.0" customHeight="1">
+    <row r="202">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -5955,7 +5955,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203" ht="15.0" customHeight="1">
+    <row r="203">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -5982,7 +5982,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204" ht="15.0" customHeight="1">
+    <row r="204">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6009,7 +6009,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205" ht="15.0" customHeight="1">
+    <row r="205">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6036,7 +6036,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206" ht="15.0" customHeight="1">
+    <row r="206">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6063,7 +6063,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207" ht="15.0" customHeight="1">
+    <row r="207">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6090,7 +6090,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208" ht="15.0" customHeight="1">
+    <row r="208">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6117,7 +6117,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209" ht="15.0" customHeight="1">
+    <row r="209">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6144,7 +6144,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210" ht="15.0" customHeight="1">
+    <row r="210">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6171,7 +6171,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211" ht="15.0" customHeight="1">
+    <row r="211">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6198,7 +6198,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212" ht="15.0" customHeight="1">
+    <row r="212">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6225,7 +6225,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213" ht="15.0" customHeight="1">
+    <row r="213">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6252,7 +6252,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214" ht="15.0" customHeight="1">
+    <row r="214">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6279,7 +6279,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215" ht="15.0" customHeight="1">
+    <row r="215">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6306,7 +6306,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216" ht="15.0" customHeight="1">
+    <row r="216">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6333,7 +6333,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217" ht="15.0" customHeight="1">
+    <row r="217">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6360,7 +6360,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218" ht="15.0" customHeight="1">
+    <row r="218">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6387,7 +6387,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219" ht="15.0" customHeight="1">
+    <row r="219">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6414,7 +6414,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220" ht="15.0" customHeight="1">
+    <row r="220">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6441,786 +6441,6 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Tables/G_ValTable.xlsx
+++ b/Tables/G_ValTable.xlsx
@@ -386,9 +386,11 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="16.75"/>
-    <col customWidth="1" min="2" max="2" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
     <col customWidth="1" min="3" max="3" width="38.75"/>
-    <col customWidth="1" min="4" max="25" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="3.25"/>
+    <col customWidth="1" min="5" max="5" width="6.88"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
